--- a/docs/supplementary_materials/table_S13_test_inventory.xlsx
+++ b/docs/supplementary_materials/table_S13_test_inventory.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$K$76</definedName>
@@ -3859,7 +3859,7 @@
     <row r="66" ht="150" customHeight="1">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>Bonferroni correction applied over the k = 55 principal inferential tests (k = 55 = 64 − 9). The 9 excluded IDs (T03, T04, T09, T10, T18, T62, T63, T64, T65) are descriptive, aggregate, or diagnostic quantities that make no inferential significance claim and are therefore not part of the multiple-testing family. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is reported as a pass-rate (5 of 6 under CellMarker, 6 of 6 under the held-out HPA reference; Figure S6, Methods), not as a single inventory p-value. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 64 tests. The nine excluded IDs are the rows carrying an em-dash in the Bonferroni p column. T11 is inside the family of 55 but reports a resampling confidence interval rather than a p-value, so it carries no corrected p; its direction robustness is given in that column instead. T44, T47 and T48 also report a raw p as a range or a bound over several sub-tests rather than as a single value, but each is corrected and capped like any other in-family row. Intermediate unharmonized values discussed in the manuscript text are documented in Table S4 rather than the unified test inventory.</t>
+          <t>Bonferroni correction applied over the k = 55 principal inferential tests (k = 55 = 64 − 9). The 9 excluded IDs (T03, T04, T09, T10, T18, T62, T63, T64, T65) are descriptive, aggregate, or diagnostic quantities that make no inferential significance claim and are therefore not part of the multiple-testing family. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is a pass-rate rather than a single inventory p-value, and is not reported in this paper. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 64 tests. The nine excluded IDs are the rows carrying an em-dash in the Bonferroni p column. T11 is inside the family of 55 but reports a resampling confidence interval rather than a p-value, so it carries no corrected p; its direction robustness is given in that column instead. T44, T47 and T48 also report a raw p as a range or a bound over several sub-tests rather than as a single value, but each is corrected and capped like any other in-family row. Intermediate unharmonized values discussed in the manuscript text are documented in S4 Table rather than the unified test inventory.</t>
         </is>
       </c>
     </row>

--- a/docs/supplementary_materials/table_S13_test_inventory.xlsx
+++ b/docs/supplementary_materials/table_S13_test_inventory.xlsx
@@ -1047,167 +1047,167 @@
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>T09</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Global coherence</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Donor-split within-species Procrustes (median of 100 splits)</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Permutation test (donor-split)</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>27–32 types per split</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>obs/null</t>
         </is>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="2" t="n">
         <v>0.375</v>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>all p &lt; 0.01 (100/100)</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>Confirmatory</t>
-        </is>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>S1 Text</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>T10</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Global coherence</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Donor-split cross-species matched Procrustes (median of 100 splits)</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Permutation test (donor-split)</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>27–32 types per split</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>obs/null</t>
         </is>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="2" t="n">
         <v>0.527</v>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>all p &lt; 0.01 (100/100)</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
-        <is>
-          <t>Confirmatory</t>
-        </is>
-      </c>
-      <c r="K11" s="19" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>S1 Text</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>T11</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Global coherence</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Donor-split delta (cross-species minus within-species)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Resampling (100 random donor splits)</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>100 splits</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>+0.159 [95% CI: +0.100, +0.218]</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>CI excludes 0 (resampling design; see Methods)</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>direction-robust (100/100; resampling)</t>
         </is>
       </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>Confirmatory</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>S1 Text</t>
         </is>
@@ -2647,302 +2647,302 @@
       </c>
     </row>
     <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>T42</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Mechanistic nulls</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Null 1: Housekeeping gene ratio</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Spearman</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>ρ</t>
         </is>
       </c>
-      <c r="G42" s="14" t="n">
+      <c r="G42" s="9" t="n">
         <v>0.167</v>
       </c>
-      <c r="H42" s="17" t="n">
+      <c r="H42" s="12" t="n">
         <v>0.337</v>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="I42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>S1 Text</t>
         </is>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>T43</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Mechanistic nulls</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Null 2: TF network complexity</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Spearman</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>ρ</t>
         </is>
       </c>
-      <c r="G43" s="14" t="n">
+      <c r="G43" s="9" t="n">
         <v>-0.229</v>
       </c>
-      <c r="H43" s="17" t="n">
+      <c r="H43" s="12" t="n">
         <v>0.185</v>
       </c>
-      <c r="I43" s="5" t="n">
+      <c r="I43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>S1 Text</t>
         </is>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>T44</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Mechanistic nulls</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Null 3: Niche adaptation gene sets (0/6 sig)</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fisher's exact + FDR</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>0/6 sig</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>0.045–1.0 (0/6 sig after FDR)</t>
         </is>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="I44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>S1 Text</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>T45</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Mechanistic nulls</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Null 4: Within-type expression variance</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Spearman</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>ρ</t>
         </is>
       </c>
-      <c r="G45" s="14" t="n">
+      <c r="G45" s="9" t="n">
         <v>-0.038</v>
       </c>
-      <c r="H45" s="17" t="n">
+      <c r="H45" s="12" t="n">
         <v>0.828</v>
       </c>
-      <c r="I45" s="5" t="n">
+      <c r="I45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>S1 Text</t>
         </is>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>T46</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Mechanistic nulls</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Null 5: Inter-donor expression variance</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Spearman</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>ρ</t>
         </is>
       </c>
-      <c r="G46" s="14" t="n">
+      <c r="G46" s="9" t="n">
         <v>-0.127</v>
       </c>
-      <c r="H46" s="17" t="n">
+      <c r="H46" s="12" t="n">
         <v>0.469</v>
       </c>
-      <c r="I46" s="5" t="n">
+      <c r="I46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>S1 Text</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>T47</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Mechanistic nulls</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Null 6: Expression-level confounds</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Spearman</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>all ρ</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>&lt; 0.21</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>all p &gt; 0.2 (11 sub-tests)</t>
         </is>
       </c>
-      <c r="I47" s="5" t="n">
+      <c r="I47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>S1 Text</t>
         </is>
@@ -3759,49 +3759,49 @@
       </c>
     </row>
     <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>T68</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Ranking validation</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Per-type residual vs marker-distinctness</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Spearman</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>ρ</t>
         </is>
       </c>
-      <c r="G64" s="9" t="n">
+      <c r="G64" s="14" t="n">
         <v>-0.136</v>
       </c>
-      <c r="H64" s="23" t="n">
+      <c r="H64" s="22" t="n">
         <v>0.4355</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I64" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>Exploratory</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>S5 Fig B</t>
         </is>

--- a/docs/supplementary_materials/table_S13_test_inventory.xlsx
+++ b/docs/supplementary_materials/table_S13_test_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S13 Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$K$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'S13 Table'!$A$1:$K$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/docs/supplementary_materials/table_S13_test_inventory.xlsx
+++ b/docs/supplementary_materials/table_S13_test_inventory.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S13 Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="S13 Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'S13 Table'!$A$1:$K$76</definedName>
@@ -3859,7 +3859,7 @@
     <row r="66" ht="150" customHeight="1">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>Bonferroni correction applied over the k = 55 principal inferential tests (k = 55 = 64 − 9). The 9 excluded IDs (T03, T04, T09, T10, T18, T62, T63, T64, T65) are descriptive, aggregate, or diagnostic quantities that make no inferential significance claim and are therefore not part of the multiple-testing family. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is a pass-rate rather than a single inventory p-value, and is not reported in this paper. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 64 tests. The nine excluded IDs are the rows carrying an em-dash in the Bonferroni p column. T11 is inside the family of 55 but reports a resampling confidence interval rather than a p-value, so it carries no corrected p; its direction robustness is given in that column instead. T44, T47 and T48 also report a raw p as a range or a bound over several sub-tests rather than as a single value, but each is corrected and capped like any other in-family row. Intermediate unharmonized values discussed in the manuscript text are documented in S4 Table rather than the unified test inventory.</t>
+          <t>Bonferroni correction applied over the k = 55 principal inferential tests (k = 55 = 64 − 9). Membership rule: a test joins the family when it yields a single p-value for a single hypothesis. The 9 excluded IDs do not. T03, T04, T09, T10 and T18 report a pass rate over repeated sub-tests (for example 100 of 100 subsamples significant) rather than one p-value for one hypothesis; their Raw p column gives that pass rate. T62, T63, T64 and T65 are descriptive or simulation-diagnostic quantities that make no inferential claim. Exclusion is a statement about the form of the result, not about whether the row is informative: several excluded rows are Confirmatory in the sense of the Status column. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is a pass-rate rather than a single inventory p-value, and is not reported in this paper. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 64 tests. The nine excluded IDs are the rows carrying an em-dash in the Bonferroni p column. Four rows are exceptions to the membership rule in the other direction, retained in the family by judgement and named here rather than left to inference. T11 reports a resampling confidence interval rather than a p-value, so it carries no corrected p; its direction robustness is given in that column instead. T44, T47 and T48 report a raw p as a range or a bound over several sub-tests rather than as a single value, but each is corrected and capped like any other in-family row. Intermediate unharmonized values discussed in the manuscript text are documented in S4 Table rather than the unified test inventory.</t>
         </is>
       </c>
     </row>

--- a/docs/supplementary_materials/table_S13_test_inventory.xlsx
+++ b/docs/supplementary_materials/table_S13_test_inventory.xlsx
@@ -3859,7 +3859,7 @@
     <row r="66" ht="150" customHeight="1">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>Bonferroni correction applied over the k = 55 principal inferential tests (k = 55 = 64 − 9). Membership rule: a test joins the family when it yields a single p-value for a single hypothesis. The 9 excluded IDs do not. T03, T04, T09, T10 and T18 report a pass rate over repeated sub-tests (for example 100 of 100 subsamples significant) rather than one p-value for one hypothesis; their Raw p column gives that pass rate. T62, T63, T64 and T65 are descriptive or simulation-diagnostic quantities that make no inferential claim. Exclusion is a statement about the form of the result, not about whether the row is informative: several excluded rows are Confirmatory in the sense of the Status column. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is a pass-rate rather than a single inventory p-value, and is not reported in this paper. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 64 tests. The nine excluded IDs are the rows carrying an em-dash in the Bonferroni p column. Four rows are exceptions to the membership rule in the other direction, retained in the family by judgement and named here rather than left to inference. T11 reports a resampling confidence interval rather than a p-value, so it carries no corrected p; its direction robustness is given in that column instead. T44, T47 and T48 report a raw p as a range or a bound over several sub-tests rather than as a single value, but each is corrected and capped like any other in-family row. Intermediate unharmonized values discussed in the manuscript text are documented in S4 Table rather than the unified test inventory.</t>
+          <t>Bonferroni correction applied over the k = 55 principal inferential tests (k = 55 = 64 − 9). Membership rule: a test joins the family when it yields a single p-value for a single hypothesis. The 9 excluded IDs do not. T03, T04, T09, T10 and T18 report a pass rate over repeated sub-tests (for example 100 of 100 subsamples significant) rather than one p-value for one hypothesis; their Raw p column gives that pass rate. T63, T64 and T65 are descriptive or simulation-diagnostic quantities that make no inferential claim. T62 is excluded on a second ground: its producer computes an asymptotic p for the full-versus-10x-only ranking correlation and S2 Fig C prints it, but the robustness claim rests on the magnitude of that correlation rather than on its difference from zero, so the p tests a hypothesis this paper does not advance. Exclusion is a statement about the form of the result, not about whether the row is informative: several excluded rows are Confirmatory in the sense of the Status column. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is a pass-rate rather than a single inventory p-value, and is not reported in this paper. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 64 tests. The nine excluded IDs are the rows carrying an em-dash in the Bonferroni p column. Four rows are exceptions to the membership rule in the other direction, retained in the family by judgement and named here rather than left to inference. T11 reports a resampling confidence interval rather than a p-value, so it carries no corrected p; its direction robustness is given in that column instead. T44, T47 and T48 report a raw p as a range or a bound over several sub-tests rather than as a single value, but each is corrected and capped like any other in-family row. Intermediate unharmonized values discussed in the manuscript text are documented in S4 Table rather than the unified test inventory.</t>
         </is>
       </c>
     </row>
